--- a/data/raw/detalles/Agencias.xlsx
+++ b/data/raw/detalles/Agencias.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Hoja1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Hoja1!$A$1:$K$166</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Hoja1!$A$1:$K$170</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="417">
   <si>
     <t>AgenciaID</t>
   </si>
@@ -210,7 +210,7 @@
     <t>SOCABAYA</t>
   </si>
   <si>
-    <t>Av. San Martin de Socabaya N° 307  - Socabaya - Arequipa</t>
+    <t>Av. San Martin de Socabaya N° 307 - Socabaya - Arequipa</t>
   </si>
   <si>
     <t>socabaya</t>
@@ -513,6 +513,12 @@
     <t>CENTRO CÍVICO</t>
   </si>
   <si>
+    <t>Av. Garcilaso de la Vega 1337</t>
+  </si>
+  <si>
+    <t>Cercado de Lima</t>
+  </si>
+  <si>
     <t>CHACLACAYO</t>
   </si>
   <si>
@@ -525,7 +531,7 @@
     <t>CHIMPU OCLLO</t>
   </si>
   <si>
-    <t>Av. Chimpu  Ocllo Mz. L-1 Lote 32 y 33, Urb. Lucyana, Carabayllo</t>
+    <t>Av. Chimpu Ocllo Mz. L-1 Lote 32 y 33, Urb. Lucyana, Carabayllo</t>
   </si>
   <si>
     <t>Carabayllo</t>
@@ -618,6 +624,15 @@
     <t>PLAZA CENTER MOQUEGUA</t>
   </si>
   <si>
+    <t>Av. Circunvalación cruce con Av. Ancash, Lt. 1-B</t>
+  </si>
+  <si>
+    <t>Moquegua</t>
+  </si>
+  <si>
+    <t>Mariscal Nieto</t>
+  </si>
+  <si>
     <t>EMANCIPACIÓN</t>
   </si>
   <si>
@@ -666,9 +681,6 @@
     <t>HUB ZARATE</t>
   </si>
   <si>
-    <t>422.86</t>
-  </si>
-  <si>
     <t>IZAGUIRRE</t>
   </si>
   <si>
@@ -690,6 +702,12 @@
     <t>LA FONTANA</t>
   </si>
   <si>
+    <t>Av. La Fontana 1065</t>
+  </si>
+  <si>
+    <t>La Molina</t>
+  </si>
+  <si>
     <t>LA PAMPILLA</t>
   </si>
   <si>
@@ -705,6 +723,9 @@
     <t>LA RAMBLA BRASIL</t>
   </si>
   <si>
+    <t>Av. Brasil 750</t>
+  </si>
+  <si>
     <t>LA SALLE</t>
   </si>
   <si>
@@ -780,6 +801,12 @@
     <t>MERCADO DE FRUTAS</t>
   </si>
   <si>
+    <t>Av. Pablo Patron 501</t>
+  </si>
+  <si>
+    <t>La Victoria</t>
+  </si>
+  <si>
     <t>MERCADO DE PRODUCTORES</t>
   </si>
   <si>
@@ -792,9 +819,6 @@
     <t>Jr. Ayacucho N° 846 - 848</t>
   </si>
   <si>
-    <t>Cercado de Lima</t>
-  </si>
-  <si>
     <t>METRO WIESSE</t>
   </si>
   <si>
@@ -948,9 +972,6 @@
     <t>PUNTO BCP IBM</t>
   </si>
   <si>
-    <t>11.36</t>
-  </si>
-  <si>
     <t>PUNTO BCP LAS VIÑAS</t>
   </si>
   <si>
@@ -966,7 +987,7 @@
     <t>PUNTO BCP SANTA CLARA</t>
   </si>
   <si>
-    <t>Centro comercial Real Plaza de Santa Clara</t>
+    <t>Av. Nicolás Ayllón 8694 y Av. La Estrella 133</t>
   </si>
   <si>
     <t>PURUCHUCO</t>
@@ -1119,12 +1140,6 @@
     <t>Torata</t>
   </si>
   <si>
-    <t>Mariscal Nieto</t>
-  </si>
-  <si>
-    <t>Moquegua</t>
-  </si>
-  <si>
     <t>ILO</t>
   </si>
   <si>
@@ -1219,13 +1234,47 @@
   </si>
   <si>
     <t>Jorge Basadre</t>
+  </si>
+  <si>
+    <t>CERCADO DE LIMA</t>
+  </si>
+  <si>
+    <t>Jr. Lampa 499</t>
+  </si>
+  <si>
+    <t>SAN BORJA AVIACIÓN</t>
+  </si>
+  <si>
+    <t>Av. Aviación 2681</t>
+  </si>
+  <si>
+    <t>San Borja</t>
+  </si>
+  <si>
+    <t>MIRAFLORES - AV. LARCO</t>
+  </si>
+  <si>
+    <t>Av. José Larco 812</t>
+  </si>
+  <si>
+    <t>Miraflores</t>
+  </si>
+  <si>
+    <t>LOS OLIVOS – MUNICIPALIDAD</t>
+  </si>
+  <si>
+    <t>Av. Carlos Izaguirre 813</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -1235,7 +1284,7 @@
     <font>
       <b/>
       <sz val="11.0"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1244,19 +1293,8 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
       <color rgb="FF1F497D"/>
       <name val="Tahoma"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1268,33 +1306,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E4E79"/>
-        <bgColor rgb="FF1E4E79"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border/>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1513,7 +1566,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="10.71"/>
-    <col customWidth="1" min="2" max="2" width="19.71"/>
+    <col customWidth="1" min="2" max="2" width="25.57"/>
     <col customWidth="1" min="3" max="3" width="14.43"/>
     <col customWidth="1" min="4" max="4" width="37.86"/>
     <col customWidth="1" min="5" max="8" width="10.71"/>
@@ -1561,29 +1614,29 @@
       <c r="A2" s="2">
         <v>200000.0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="3">
+      <c r="H2" s="4"/>
+      <c r="I2" s="5">
         <v>29402.0</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K2" s="2">
@@ -1594,31 +1647,31 @@
       <c r="A3" s="2">
         <v>205000.0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="2">
         <v>479.97</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="5">
         <v>36409.0</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="2">
@@ -1629,29 +1682,29 @@
       <c r="A4" s="2">
         <v>215000.0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="2">
         <v>5336.64</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="2" t="s">
+      <c r="I4" s="6"/>
+      <c r="J4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K4" s="2">
@@ -1662,31 +1715,31 @@
       <c r="A5" s="2">
         <v>215010.0</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="2">
         <v>452.0</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="7">
         <v>39695.0</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K5" s="2">
@@ -1697,29 +1750,29 @@
       <c r="A6" s="2">
         <v>250000.0</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H6" s="2">
         <v>308.54</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="2" t="s">
+      <c r="I6" s="6"/>
+      <c r="J6" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K6" s="2">
@@ -1730,29 +1783,29 @@
       <c r="A7" s="2">
         <v>215002.0</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H7" s="2">
         <v>800.6</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="2" t="s">
+      <c r="I7" s="6"/>
+      <c r="J7" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K7" s="2">
@@ -1763,31 +1816,31 @@
       <c r="A8" s="2">
         <v>215013.0</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H8" s="2">
         <v>542.65</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="7">
         <v>41492.0</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K8" s="2">
@@ -1798,31 +1851,31 @@
       <c r="A9" s="2">
         <v>251000.0</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H9" s="2">
         <v>320.0</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="7">
         <v>39689.0</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K9" s="2">
@@ -1833,29 +1886,29 @@
       <c r="A10" s="2">
         <v>425000.0</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H10" s="2">
         <v>427.11</v>
       </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="2" t="s">
+      <c r="I10" s="6"/>
+      <c r="J10" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K10" s="2">
@@ -1866,31 +1919,31 @@
       <c r="A11" s="2">
         <v>215022.0</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H11" s="2">
         <v>256.33</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="7">
         <v>42107.0</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K11" s="2">
@@ -1901,29 +1954,29 @@
       <c r="A12" s="2">
         <v>215003.0</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H12" s="2">
         <v>423.98</v>
       </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="2" t="s">
+      <c r="I12" s="6"/>
+      <c r="J12" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K12" s="2">
@@ -1934,29 +1987,29 @@
       <c r="A13" s="2">
         <v>215004.0</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="2">
         <v>807.33</v>
       </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="2" t="s">
+      <c r="I13" s="6"/>
+      <c r="J13" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K13" s="2">
@@ -1967,31 +2020,31 @@
       <c r="A14" s="2">
         <v>215011.0</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H14" s="2">
         <v>350.0</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="7">
         <v>40609.0</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K14" s="2">
@@ -2002,31 +2055,31 @@
       <c r="A15" s="2">
         <v>215014.0</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H15" s="2">
         <v>1232.0</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="8">
         <v>41625.0</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K15" s="2">
@@ -2037,29 +2090,29 @@
       <c r="A16" s="2">
         <v>215005.0</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H16" s="2">
         <v>353.0</v>
       </c>
-      <c r="I16" s="3"/>
-      <c r="J16" s="2" t="s">
+      <c r="I16" s="6"/>
+      <c r="J16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K16" s="2">
@@ -2070,31 +2123,31 @@
       <c r="A17" s="2">
         <v>215006.0</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H17" s="2">
         <v>615.88</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="7">
         <v>32209.0</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K17" s="2">
@@ -2105,31 +2158,31 @@
       <c r="A18" s="2">
         <v>215015.0</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="2">
         <v>1130.87</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="8">
         <v>41932.0</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K18" s="2">
@@ -2140,29 +2193,29 @@
       <c r="A19" s="2">
         <v>215017.0</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="3">
+      <c r="H19" s="6"/>
+      <c r="I19" s="8">
         <v>42286.0</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K19" s="2">
@@ -2173,31 +2226,31 @@
       <c r="A20" s="2">
         <v>215009.0</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H20" s="2">
         <v>318.0</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="8">
         <v>39021.0</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K20" s="2">
@@ -2208,31 +2261,31 @@
       <c r="A21" s="2">
         <v>220000.0</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="3" t="s">
         <v>72</v>
       </c>
       <c r="H21" s="2">
         <v>2556.35</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="7">
         <v>35255.0</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K21" s="2">
@@ -2243,31 +2296,31 @@
       <c r="A22" s="2">
         <v>220002.0</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="3" t="s">
         <v>72</v>
       </c>
       <c r="H22" s="2">
         <v>388.92</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="7">
         <v>42373.0</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K22" s="2">
@@ -2278,31 +2331,31 @@
       <c r="A23" s="2">
         <v>285000.0</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="3" t="s">
         <v>78</v>
       </c>
       <c r="H23" s="2">
         <v>1602.88</v>
       </c>
-      <c r="I23" s="3">
+      <c r="I23" s="7">
         <v>36923.0</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K23" s="2">
@@ -2313,31 +2366,31 @@
       <c r="A24" s="2">
         <v>285003.0</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="3" t="s">
         <v>78</v>
       </c>
       <c r="H24" s="2">
         <v>350.56</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="7">
         <v>36621.0</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K24" s="2">
@@ -2348,31 +2401,31 @@
       <c r="A25" s="2">
         <v>285004.0</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="3" t="s">
         <v>78</v>
       </c>
       <c r="H25" s="2">
         <v>19.8</v>
       </c>
-      <c r="I25" s="3">
+      <c r="I25" s="7">
         <v>38755.0</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K25" s="2">
@@ -2383,31 +2436,31 @@
       <c r="A26" s="2">
         <v>285008.0</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="3" t="s">
         <v>78</v>
       </c>
       <c r="H26" s="2">
         <v>497.09</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I26" s="8">
         <v>41551.0</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K26" s="2">
@@ -2418,31 +2471,31 @@
       <c r="A27" s="2">
         <v>285009.0</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="3" t="s">
         <v>78</v>
       </c>
       <c r="H27" s="2">
         <v>682.0</v>
       </c>
-      <c r="I27" s="3">
+      <c r="I27" s="7">
         <v>41284.0</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J27" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K27" s="2">
@@ -2453,31 +2506,31 @@
       <c r="A28" s="2">
         <v>285006.0</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="3" t="s">
         <v>78</v>
       </c>
       <c r="H28" s="2">
         <v>300.0</v>
       </c>
-      <c r="I28" s="3">
+      <c r="I28" s="7">
         <v>39833.0</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K28" s="2">
@@ -2488,31 +2541,31 @@
       <c r="A29" s="2">
         <v>285005.0</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="3" t="s">
         <v>78</v>
       </c>
       <c r="H29" s="2">
         <v>770.58</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="7">
         <v>38796.0</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="J29" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K29" s="2">
@@ -2523,31 +2576,31 @@
       <c r="A30" s="2">
         <v>285007.0</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="3" t="s">
         <v>78</v>
       </c>
       <c r="H30" s="2">
         <v>159.13</v>
       </c>
-      <c r="I30" s="3">
+      <c r="I30" s="7">
         <v>40794.0</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="J30" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K30" s="2">
@@ -2558,31 +2611,31 @@
       <c r="A31" s="2">
         <v>505000.0</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="3" t="s">
         <v>78</v>
       </c>
       <c r="H31" s="2">
         <v>257.0</v>
       </c>
-      <c r="I31" s="3">
+      <c r="I31" s="7">
         <v>36176.0</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="J31" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K31" s="2">
@@ -2593,31 +2646,31 @@
       <c r="A32" s="2">
         <v>285011.0</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="3" t="s">
         <v>78</v>
       </c>
       <c r="H32" s="2">
         <v>323.59</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="7">
         <v>41668.0</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="J32" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K32" s="2">
@@ -2628,31 +2681,31 @@
       <c r="A33" s="2">
         <v>533000.0</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="3" t="s">
         <v>78</v>
       </c>
       <c r="H33" s="2">
         <v>190.0</v>
       </c>
-      <c r="I33" s="3">
+      <c r="I33" s="7">
         <v>39611.0</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="J33" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K33" s="2">
@@ -2663,29 +2716,29 @@
       <c r="A34" s="2">
         <v>315000.0</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="C34" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="3" t="s">
         <v>112</v>
       </c>
       <c r="H34" s="2">
         <v>1162.08</v>
       </c>
-      <c r="I34" s="3"/>
-      <c r="J34" s="2" t="s">
+      <c r="I34" s="6"/>
+      <c r="J34" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K34" s="2">
@@ -2696,31 +2749,31 @@
       <c r="A35" s="2">
         <v>315001.0</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="C35" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="3" t="s">
         <v>112</v>
       </c>
       <c r="H35" s="2">
         <v>975.15</v>
       </c>
-      <c r="I35" s="3">
+      <c r="I35" s="7">
         <v>35579.0</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="J35" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K35" s="2">
@@ -2731,31 +2784,31 @@
       <c r="A36" s="2">
         <v>513000.0</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="C36" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="3" t="s">
         <v>112</v>
       </c>
       <c r="H36" s="2">
         <v>305.67</v>
       </c>
-      <c r="I36" s="3">
+      <c r="I36" s="7">
         <v>25055.0</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="J36" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K36" s="2">
@@ -2766,29 +2819,29 @@
       <c r="A37" s="2">
         <v>380008.0</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="C37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="H37" s="2"/>
-      <c r="I37" s="3">
+      <c r="H37" s="6"/>
+      <c r="I37" s="7">
         <v>41648.0</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="J37" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K37" s="2">
@@ -2799,29 +2852,29 @@
       <c r="A38" s="2">
         <v>440000.0</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="C38" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="3" t="s">
         <v>112</v>
       </c>
       <c r="H38" s="2">
         <v>336.0</v>
       </c>
-      <c r="I38" s="3"/>
-      <c r="J38" s="2" t="s">
+      <c r="I38" s="6"/>
+      <c r="J38" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K38" s="2">
@@ -2832,29 +2885,29 @@
       <c r="A39" s="2">
         <v>470000.0</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="C39" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="3" t="s">
         <v>112</v>
       </c>
       <c r="H39" s="2">
         <v>985.63</v>
       </c>
-      <c r="I39" s="3"/>
-      <c r="J39" s="2" t="s">
+      <c r="I39" s="6"/>
+      <c r="J39" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K39" s="2">
@@ -2865,29 +2918,29 @@
       <c r="A40" s="2">
         <v>380000.0</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="C40" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="3" t="s">
         <v>112</v>
       </c>
       <c r="H40" s="2">
         <v>1518.25</v>
       </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="2" t="s">
+      <c r="I40" s="6"/>
+      <c r="J40" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K40" s="2">
@@ -2898,31 +2951,31 @@
       <c r="A41" s="2">
         <v>380004.0</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="C41" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="3" t="s">
         <v>112</v>
       </c>
       <c r="H41" s="2">
         <v>292.3</v>
       </c>
-      <c r="I41" s="3">
+      <c r="I41" s="7">
         <v>39113.0</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="J41" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K41" s="2">
@@ -2933,31 +2986,31 @@
       <c r="A42" s="2">
         <v>380007.0</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="C42" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="3" t="s">
         <v>112</v>
       </c>
       <c r="H42" s="2">
         <v>528.0</v>
       </c>
-      <c r="I42" s="3">
+      <c r="I42" s="7">
         <v>41106.0</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="J42" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K42" s="2">
@@ -2968,25 +3021,25 @@
       <c r="A43" s="2">
         <v>191089.0</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2" t="s">
+      <c r="C43" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D43" s="6"/>
+      <c r="E43" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H43" s="2"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="2" t="s">
+      <c r="F43" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K43" s="2">
@@ -2997,31 +3050,31 @@
       <c r="A44" s="2">
         <v>191057.0</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="C44" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G44" s="2" t="s">
+      <c r="F44" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H44" s="2">
         <v>382.37</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="8">
         <v>41211.0</v>
       </c>
-      <c r="J44" s="2" t="s">
+      <c r="J44" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K44" s="2">
@@ -3032,31 +3085,31 @@
       <c r="A45" s="2">
         <v>191028.0</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="C45" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F45" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G45" s="2" t="s">
+      <c r="F45" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G45" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H45" s="2">
         <v>327.2</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="7">
         <v>38243.0</v>
       </c>
-      <c r="J45" s="2" t="s">
+      <c r="J45" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K45" s="2">
@@ -3067,31 +3120,31 @@
       <c r="A46" s="2">
         <v>191014.0</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="C46" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G46" s="2" t="s">
+      <c r="E46" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G46" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H46" s="2">
         <v>570.0</v>
       </c>
-      <c r="I46" s="3">
+      <c r="I46" s="7">
         <v>27395.0</v>
       </c>
-      <c r="J46" s="2" t="s">
+      <c r="J46" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K46" s="2">
@@ -3102,31 +3155,31 @@
       <c r="A47" s="2">
         <v>194038.0</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D47" s="2" t="s">
+      <c r="C47" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="3" t="s">
         <v>147</v>
       </c>
       <c r="H47" s="2">
         <v>200.0</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="8">
         <v>42723.0</v>
       </c>
-      <c r="J47" s="2" t="s">
+      <c r="J47" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K47" s="2">
@@ -3137,31 +3190,31 @@
       <c r="A48" s="2">
         <v>191018.0</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="C48" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F48" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G48" s="2" t="s">
+      <c r="F48" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G48" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H48" s="2">
         <v>228.0</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="7">
         <v>37713.0</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="J48" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K48" s="2">
@@ -3172,31 +3225,31 @@
       <c r="A49" s="2">
         <v>191098.0</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="C49" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G49" s="2" t="s">
+      <c r="E49" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G49" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H49" s="2">
         <v>270.0</v>
       </c>
-      <c r="I49" s="3">
+      <c r="I49" s="8">
         <v>39728.0</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="J49" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K49" s="2">
@@ -3207,31 +3260,31 @@
       <c r="A50" s="2">
         <v>191096.0</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="C50" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G50" s="2" t="s">
+      <c r="F50" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G50" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H50" s="2">
         <v>247.0</v>
       </c>
-      <c r="I50" s="3">
+      <c r="I50" s="7">
         <v>37881.0</v>
       </c>
-      <c r="J50" s="2" t="s">
+      <c r="J50" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K50" s="2">
@@ -3242,31 +3295,31 @@
       <c r="A51" s="2">
         <v>191095.0</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="C51" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G51" s="2" t="s">
+      <c r="E51" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G51" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H51" s="2">
         <v>150.87</v>
       </c>
-      <c r="I51" s="3">
+      <c r="I51" s="7">
         <v>37803.0</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="J51" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K51" s="2">
@@ -3277,31 +3330,31 @@
       <c r="A52" s="2">
         <v>191091.0</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="C52" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G52" s="2" t="s">
+      <c r="F52" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G52" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H52" s="2">
         <v>113.76</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="8">
         <v>38342.0</v>
       </c>
-      <c r="J52" s="2" t="s">
+      <c r="J52" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K52" s="2">
@@ -3312,21 +3365,21 @@
       <c r="A53" s="2">
         <v>100001.0</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H53" s="2"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="2" t="s">
+      <c r="C53" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K53" s="2">
@@ -3337,31 +3390,31 @@
       <c r="A54" s="2">
         <v>255000.0</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" s="2" t="s">
+      <c r="C54" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H54" s="2">
         <v>550.21</v>
       </c>
-      <c r="I54" s="3">
+      <c r="I54" s="8">
         <v>36102.0</v>
       </c>
-      <c r="J54" s="2" t="s">
+      <c r="J54" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K54" s="2">
@@ -3372,22 +3425,28 @@
       <c r="A55" s="2">
         <v>191105.0</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H55" s="2"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="2" t="s">
-        <v>136</v>
+      <c r="C55" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="3" t="s">
+        <v>1</v>
       </c>
       <c r="K55" s="2">
         <v>4.0</v>
@@ -3397,31 +3456,31 @@
       <c r="A56" s="2">
         <v>191074.0</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="B56" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G56" s="2" t="s">
+      <c r="C56" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G56" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H56" s="2">
         <v>320.0</v>
       </c>
-      <c r="I56" s="3">
+      <c r="I56" s="7">
         <v>39570.0</v>
       </c>
-      <c r="J56" s="2" t="s">
+      <c r="J56" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K56" s="2">
@@ -3432,31 +3491,31 @@
       <c r="A57" s="2">
         <v>191113.0</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E57" s="2" t="s">
+      <c r="B57" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G57" s="2" t="s">
+      <c r="C57" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G57" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H57" s="2">
         <v>360.0</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="8">
         <v>40893.0</v>
       </c>
-      <c r="J57" s="2" t="s">
+      <c r="J57" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K57" s="2">
@@ -3467,31 +3526,31 @@
       <c r="A58" s="2">
         <v>191075.0</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="B58" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G58" s="2" t="s">
+      <c r="C58" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G58" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H58" s="2">
         <v>321.93</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I58" s="8">
         <v>21524.0</v>
       </c>
-      <c r="J58" s="2" t="s">
+      <c r="J58" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K58" s="2">
@@ -3502,31 +3561,31 @@
       <c r="A59" s="2">
         <v>191065.0</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E59" s="2" t="s">
+      <c r="B59" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G59" s="2" t="s">
+      <c r="F59" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G59" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H59" s="2">
         <v>320.0</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="7">
         <v>39631.0</v>
       </c>
-      <c r="J59" s="2" t="s">
+      <c r="J59" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K59" s="2">
@@ -3537,25 +3596,25 @@
       <c r="A60" s="2">
         <v>192035.0</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F60" s="2" t="s">
+      <c r="B60" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H60" s="2"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="2" t="s">
+      <c r="C60" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D60" s="6"/>
+      <c r="E60" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K60" s="2">
@@ -3566,21 +3625,21 @@
       <c r="A61" s="2">
         <v>193005.0</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H61" s="2"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="2" t="s">
+      <c r="B61" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K61" s="2">
@@ -3591,31 +3650,31 @@
       <c r="A62" s="2">
         <v>255001.0</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E62" s="2" t="s">
+      <c r="B62" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="C62" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G62" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H62" s="2">
         <v>323.6</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="7">
         <v>40071.0</v>
       </c>
-      <c r="J62" s="2" t="s">
+      <c r="J62" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K62" s="2">
@@ -3626,21 +3685,21 @@
       <c r="A63" s="2">
         <v>193064.0</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H63" s="2"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="2" t="s">
+      <c r="B63" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K63" s="2">
@@ -3651,31 +3710,31 @@
       <c r="A64" s="2">
         <v>191041.0</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E64" s="2" t="s">
+      <c r="B64" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G64" s="2" t="s">
+      <c r="C64" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G64" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H64" s="2">
         <v>318.0</v>
       </c>
-      <c r="I64" s="3">
+      <c r="I64" s="7">
         <v>39511.0</v>
       </c>
-      <c r="J64" s="2" t="s">
+      <c r="J64" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K64" s="2">
@@ -3686,31 +3745,31 @@
       <c r="A65" s="2">
         <v>255002.0</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="B65" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="C65" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H65" s="2">
         <v>232.0</v>
       </c>
-      <c r="I65" s="3">
+      <c r="I65" s="7">
         <v>39233.0</v>
       </c>
-      <c r="J65" s="2" t="s">
+      <c r="J65" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K65" s="2">
@@ -3721,31 +3780,31 @@
       <c r="A66" s="2">
         <v>191087.0</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E66" s="2" t="s">
+      <c r="B66" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G66" s="2" t="s">
+      <c r="C66" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G66" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H66" s="2">
         <v>353.1</v>
       </c>
-      <c r="I66" s="3">
+      <c r="I66" s="8">
         <v>31401.0</v>
       </c>
-      <c r="J66" s="2" t="s">
+      <c r="J66" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K66" s="2">
@@ -3756,31 +3815,31 @@
       <c r="A67" s="2">
         <v>191037.0</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G67" s="2" t="s">
+      <c r="B67" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G67" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H67" s="2">
         <v>196.23</v>
       </c>
-      <c r="I67" s="3">
+      <c r="I67" s="7">
         <v>38366.0</v>
       </c>
-      <c r="J67" s="2" t="s">
+      <c r="J67" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K67" s="2">
@@ -3791,31 +3850,31 @@
       <c r="A68" s="2">
         <v>191082.0</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E68" s="2" t="s">
+      <c r="B68" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G68" s="2" t="s">
+      <c r="F68" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G68" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H68" s="2">
         <v>706.49</v>
       </c>
-      <c r="I68" s="3">
+      <c r="I68" s="8">
         <v>41218.0</v>
       </c>
-      <c r="J68" s="2" t="s">
+      <c r="J68" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K68" s="2">
@@ -3826,31 +3885,31 @@
       <c r="A69" s="2">
         <v>191067.0</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G69" s="2" t="s">
+      <c r="B69" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G69" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H69" s="2">
         <v>288.7</v>
       </c>
-      <c r="I69" s="3">
+      <c r="I69" s="7">
         <v>18264.0</v>
       </c>
-      <c r="J69" s="2" t="s">
+      <c r="J69" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K69" s="2">
@@ -3861,22 +3920,28 @@
       <c r="A70" s="2">
         <v>100003.0</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H70" s="2"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="2" t="s">
-        <v>136</v>
+      <c r="B70" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="K70" s="2">
         <v>2.0</v>
@@ -3886,31 +3951,31 @@
       <c r="A71" s="2">
         <v>191054.0</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G71" s="2" t="s">
+      <c r="B71" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G71" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H71" s="2">
         <v>417.18</v>
       </c>
-      <c r="I71" s="3">
+      <c r="I71" s="7">
         <v>39689.0</v>
       </c>
-      <c r="J71" s="2" t="s">
+      <c r="J71" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K71" s="2">
@@ -3921,25 +3986,25 @@
       <c r="A72" s="2">
         <v>100004.0</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2" t="s">
+      <c r="B72" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H72" s="2">
         <v>50.0</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="7">
         <v>41306.0</v>
       </c>
-      <c r="J72" s="2" t="s">
+      <c r="J72" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K72" s="2">
@@ -3950,32 +4015,32 @@
       <c r="A73" s="2">
         <v>191088.0</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G73" s="2" t="s">
+      <c r="B73" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G73" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H73" s="2">
         <v>600.0</v>
       </c>
-      <c r="I73" s="3">
+      <c r="I73" s="7">
         <v>36540.0</v>
       </c>
-      <c r="J73" s="2" t="s">
-        <v>207</v>
+      <c r="J73" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="K73" s="2">
         <v>4.0</v>
@@ -3985,21 +4050,21 @@
       <c r="A74" s="2">
         <v>191005.0</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H74" s="2"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="2" t="s">
+      <c r="B74" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K74" s="2">
@@ -4010,31 +4075,31 @@
       <c r="A75" s="2">
         <v>191023.0</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G75" s="2" t="s">
+      <c r="B75" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G75" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H75" s="2">
         <v>274.0</v>
       </c>
-      <c r="I75" s="3">
+      <c r="I75" s="8">
         <v>37949.0</v>
       </c>
-      <c r="J75" s="2" t="s">
+      <c r="J75" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K75" s="2">
@@ -4045,31 +4110,31 @@
       <c r="A76" s="2">
         <v>191085.0</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G76" s="2" t="s">
+      <c r="B76" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G76" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H76" s="2">
         <v>320.0</v>
       </c>
-      <c r="I76" s="3">
+      <c r="I76" s="8">
         <v>38701.0</v>
       </c>
-      <c r="J76" s="2" t="s">
+      <c r="J76" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K76" s="2">
@@ -4080,31 +4145,31 @@
       <c r="A77" s="2">
         <v>191174.0</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G77" s="2" t="s">
+      <c r="B77" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G77" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H77" s="2">
         <v>228.1</v>
       </c>
-      <c r="I77" s="3">
+      <c r="I77" s="7">
         <v>42009.0</v>
       </c>
-      <c r="J77" s="2" t="s">
+      <c r="J77" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K77" s="2">
@@ -4115,25 +4180,25 @@
       <c r="A78" s="2">
         <v>100005.0</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="I78" s="4">
+      <c r="B78" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H78" s="3">
+        <v>422.86</v>
+      </c>
+      <c r="I78" s="9">
         <v>38180.0</v>
       </c>
-      <c r="J78" s="2" t="s">
+      <c r="J78" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K78" s="2">
@@ -4144,31 +4209,31 @@
       <c r="A79" s="2">
         <v>191154.0</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E79" s="2" t="s">
+      <c r="B79" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G79" s="2" t="s">
+      <c r="F79" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G79" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H79" s="2">
         <v>494.71</v>
       </c>
-      <c r="I79" s="3">
+      <c r="I79" s="7">
         <v>42079.0</v>
       </c>
-      <c r="J79" s="2" t="s">
+      <c r="J79" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K79" s="2">
@@ -4179,31 +4244,31 @@
       <c r="A80" s="2">
         <v>191165.0</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G80" s="2" t="s">
+      <c r="B80" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G80" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H80" s="2">
         <v>108.2</v>
       </c>
-      <c r="I80" s="3">
+      <c r="I80" s="8">
         <v>41990.0</v>
       </c>
-      <c r="J80" s="2" t="s">
+      <c r="J80" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K80" s="2">
@@ -4214,31 +4279,31 @@
       <c r="A81" s="2">
         <v>191148.0</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E81" s="2" t="s">
+      <c r="B81" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F81" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G81" s="2" t="s">
+      <c r="F81" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G81" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H81" s="2">
         <v>491.59</v>
       </c>
-      <c r="I81" s="3">
+      <c r="I81" s="7">
         <v>41494.0</v>
       </c>
-      <c r="J81" s="2" t="s">
+      <c r="J81" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K81" s="2">
@@ -4249,21 +4314,27 @@
       <c r="A82" s="2">
         <v>193054.0</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H82" s="2"/>
-      <c r="I82" s="3"/>
-      <c r="J82" s="2" t="s">
+      <c r="B82" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K82" s="2">
@@ -4274,32 +4345,32 @@
       <c r="A83" s="2">
         <v>192012.0</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G83" s="2" t="s">
+      <c r="B83" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G83" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H83" s="2">
         <v>60.0</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="7">
         <v>35944.0</v>
       </c>
-      <c r="J83" s="2" t="s">
-        <v>227</v>
+      <c r="J83" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="K83" s="2">
         <v>4.0</v>
@@ -4309,21 +4380,21 @@
       <c r="A84" s="2">
         <v>193045.0</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H84" s="2"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="2" t="s">
+      <c r="B84" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K84" s="2">
@@ -4334,21 +4405,27 @@
       <c r="A85" s="2">
         <v>191166.0</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H85" s="2"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="2" t="s">
+      <c r="B85" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K85" s="2">
@@ -4359,21 +4436,21 @@
       <c r="A86" s="2">
         <v>191114.0</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H86" s="2"/>
-      <c r="I86" s="3"/>
-      <c r="J86" s="2" t="s">
+      <c r="B86" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6"/>
+      <c r="J86" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K86" s="2">
@@ -4384,31 +4461,31 @@
       <c r="A87" s="2">
         <v>191044.0</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G87" s="2" t="s">
+      <c r="B87" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G87" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H87" s="2">
         <v>228.0</v>
       </c>
-      <c r="I87" s="3">
+      <c r="I87" s="7">
         <v>39293.0</v>
       </c>
-      <c r="J87" s="2" t="s">
+      <c r="J87" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K87" s="2">
@@ -4419,31 +4496,31 @@
       <c r="A88" s="2">
         <v>191055.0</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E88" s="2" t="s">
+      <c r="B88" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G88" s="2" t="s">
+      <c r="F88" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G88" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H88" s="2">
         <v>381.24</v>
       </c>
-      <c r="I88" s="3">
+      <c r="I88" s="7">
         <v>39707.0</v>
       </c>
-      <c r="J88" s="2" t="s">
+      <c r="J88" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K88" s="2">
@@ -4454,31 +4531,31 @@
       <c r="A89" s="2">
         <v>191076.0</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G89" s="2" t="s">
+      <c r="B89" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G89" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H89" s="2">
         <v>441.58</v>
       </c>
-      <c r="I89" s="3">
+      <c r="I89" s="7">
         <v>39640.0</v>
       </c>
-      <c r="J89" s="2" t="s">
+      <c r="J89" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K89" s="2">
@@ -4489,31 +4566,31 @@
       <c r="A90" s="2">
         <v>191080.0</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G90" s="2" t="s">
+      <c r="B90" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G90" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H90" s="2">
         <v>228.82</v>
       </c>
-      <c r="I90" s="3">
+      <c r="I90" s="8">
         <v>39791.0</v>
       </c>
-      <c r="J90" s="2" t="s">
+      <c r="J90" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K90" s="2">
@@ -4524,21 +4601,21 @@
       <c r="A91" s="2">
         <v>193038.0</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H91" s="2"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="2" t="s">
+      <c r="B91" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K91" s="2">
@@ -4549,31 +4626,31 @@
       <c r="A92" s="2">
         <v>191115.0</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G92" s="2" t="s">
+      <c r="B92" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G92" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H92" s="2">
         <v>610.55</v>
       </c>
-      <c r="I92" s="3">
+      <c r="I92" s="7">
         <v>41114.0</v>
       </c>
-      <c r="J92" s="2" t="s">
+      <c r="J92" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K92" s="2">
@@ -4584,31 +4661,31 @@
       <c r="A93" s="2">
         <v>191118.0</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G93" s="2" t="s">
+      <c r="B93" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G93" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H93" s="2">
         <v>484.45</v>
       </c>
-      <c r="I93" s="3">
+      <c r="I93" s="7">
         <v>41156.0</v>
       </c>
-      <c r="J93" s="2" t="s">
+      <c r="J93" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K93" s="2">
@@ -4619,31 +4696,31 @@
       <c r="A94" s="2">
         <v>191010.0</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D94" s="2" t="s">
+      <c r="B94" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G94" s="2" t="s">
+      <c r="F94" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G94" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H94" s="2">
         <v>365.0</v>
       </c>
-      <c r="I94" s="3">
+      <c r="I94" s="8">
         <v>37590.0</v>
       </c>
-      <c r="J94" s="2" t="s">
+      <c r="J94" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K94" s="2">
@@ -4654,31 +4731,31 @@
       <c r="A95" s="2">
         <v>191040.0</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G95" s="2" t="s">
+      <c r="B95" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G95" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H95" s="2">
         <v>291.92</v>
       </c>
-      <c r="I95" s="3">
+      <c r="I95" s="7">
         <v>39212.0</v>
       </c>
-      <c r="J95" s="2" t="s">
+      <c r="J95" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K95" s="2">
@@ -4689,31 +4766,31 @@
       <c r="A96" s="2">
         <v>191078.0</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E96" s="2" t="s">
+      <c r="B96" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F96" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G96" s="2" t="s">
+      <c r="F96" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G96" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H96" s="2">
         <v>384.3</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="7">
         <v>30195.0</v>
       </c>
-      <c r="J96" s="2" t="s">
+      <c r="J96" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K96" s="2">
@@ -4724,31 +4801,31 @@
       <c r="A97" s="2">
         <v>191002.0</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G97" s="2" t="s">
+      <c r="B97" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G97" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H97" s="2">
         <v>436.5</v>
       </c>
-      <c r="I97" s="3">
+      <c r="I97" s="8">
         <v>27325.0</v>
       </c>
-      <c r="J97" s="2" t="s">
+      <c r="J97" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K97" s="2">
@@ -4759,21 +4836,27 @@
       <c r="A98" s="2">
         <v>191064.0</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H98" s="2"/>
-      <c r="I98" s="3"/>
-      <c r="J98" s="2" t="s">
+      <c r="B98" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K98" s="2">
@@ -4784,31 +4867,31 @@
       <c r="A99" s="2">
         <v>191061.0</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G99" s="2" t="s">
+      <c r="B99" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G99" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H99" s="2">
         <v>226.0</v>
       </c>
-      <c r="I99" s="3">
+      <c r="I99" s="8">
         <v>39765.0</v>
       </c>
-      <c r="J99" s="2" t="s">
+      <c r="J99" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K99" s="2">
@@ -4819,31 +4902,31 @@
       <c r="A100" s="2">
         <v>191069.0</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G100" s="2" t="s">
+      <c r="B100" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G100" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H100" s="2">
         <v>350.0</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="7">
         <v>39567.0</v>
       </c>
-      <c r="J100" s="2" t="s">
+      <c r="J100" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K100" s="2">
@@ -4854,31 +4937,31 @@
       <c r="A101" s="2">
         <v>191106.0</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E101" s="2" t="s">
+      <c r="B101" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F101" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G101" s="2" t="s">
+      <c r="F101" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G101" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H101" s="2">
         <v>244.7</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="7">
         <v>40638.0</v>
       </c>
-      <c r="J101" s="2" t="s">
+      <c r="J101" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K101" s="2">
@@ -4889,21 +4972,21 @@
       <c r="A102" s="2">
         <v>193004.0</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H102" s="2"/>
-      <c r="I102" s="3"/>
-      <c r="J102" s="2" t="s">
+      <c r="B102" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K102" s="2">
@@ -4914,31 +4997,31 @@
       <c r="A103" s="2">
         <v>191077.0</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G103" s="2" t="s">
+      <c r="B103" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G103" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H103" s="2">
         <v>378.89</v>
       </c>
-      <c r="I103" s="3">
+      <c r="I103" s="7">
         <v>39261.0</v>
       </c>
-      <c r="J103" s="2" t="s">
+      <c r="J103" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K103" s="2">
@@ -4949,31 +5032,31 @@
       <c r="A104" s="2">
         <v>191142.0</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G104" s="2" t="s">
+      <c r="B104" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G104" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H104" s="2">
         <v>933.08</v>
       </c>
-      <c r="I104" s="3">
+      <c r="I104" s="7">
         <v>41645.0</v>
       </c>
-      <c r="J104" s="2" t="s">
+      <c r="J104" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K104" s="2">
@@ -4984,21 +5067,21 @@
       <c r="A105" s="2">
         <v>193050.0</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H105" s="2"/>
-      <c r="I105" s="3"/>
-      <c r="J105" s="2" t="s">
+      <c r="B105" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K105" s="2">
@@ -5009,31 +5092,31 @@
       <c r="A106" s="2">
         <v>191084.0</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G106" s="2" t="s">
+      <c r="B106" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G106" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H106" s="2">
         <v>545.4</v>
       </c>
-      <c r="I106" s="3">
+      <c r="I106" s="7">
         <v>19360.0</v>
       </c>
-      <c r="J106" s="2" t="s">
+      <c r="J106" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K106" s="2">
@@ -5044,31 +5127,31 @@
       <c r="A107" s="2">
         <v>191141.0</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E107" s="2" t="s">
+      <c r="B107" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F107" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G107" s="2" t="s">
+      <c r="F107" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G107" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H107" s="2">
         <v>708.45</v>
       </c>
-      <c r="I107" s="3">
+      <c r="I107" s="7">
         <v>41277.0</v>
       </c>
-      <c r="J107" s="2" t="s">
+      <c r="J107" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K107" s="2">
@@ -5079,31 +5162,31 @@
       <c r="A108" s="2">
         <v>191143.0</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E108" s="2" t="s">
+      <c r="B108" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E108" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F108" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G108" s="2" t="s">
+      <c r="F108" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G108" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H108" s="2">
         <v>364.25</v>
       </c>
-      <c r="I108" s="3">
+      <c r="I108" s="7">
         <v>41723.0</v>
       </c>
-      <c r="J108" s="2" t="s">
+      <c r="J108" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K108" s="2">
@@ -5114,31 +5197,31 @@
       <c r="A109" s="2">
         <v>191027.0</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G109" s="2" t="s">
+      <c r="B109" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G109" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H109" s="2">
         <v>333.45</v>
       </c>
-      <c r="I109" s="3">
+      <c r="I109" s="7">
         <v>29402.0</v>
       </c>
-      <c r="J109" s="2" t="s">
+      <c r="J109" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K109" s="2">
@@ -5149,31 +5232,31 @@
       <c r="A110" s="2">
         <v>191047.0</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G110" s="2" t="s">
+      <c r="B110" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G110" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H110" s="2">
         <v>129.43</v>
       </c>
-      <c r="I110" s="3">
+      <c r="I110" s="7">
         <v>23437.0</v>
       </c>
-      <c r="J110" s="2" t="s">
+      <c r="J110" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K110" s="2">
@@ -5184,32 +5267,32 @@
       <c r="A111" s="2">
         <v>191157.0</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G111" s="2" t="s">
+      <c r="B111" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G111" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H111" s="2">
         <v>10.0</v>
       </c>
-      <c r="I111" s="3">
+      <c r="I111" s="7">
         <v>41673.0</v>
       </c>
-      <c r="J111" s="2" t="s">
-        <v>227</v>
+      <c r="J111" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="K111" s="2">
         <v>4.0</v>
@@ -5219,32 +5302,32 @@
       <c r="A112" s="2">
         <v>191163.0</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G112" s="2" t="s">
+      <c r="B112" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G112" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H112" s="2">
         <v>12.0</v>
       </c>
-      <c r="I112" s="3">
+      <c r="I112" s="7">
         <v>41788.0</v>
       </c>
-      <c r="J112" s="2" t="s">
-        <v>227</v>
+      <c r="J112" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="K112" s="2">
         <v>4.0</v>
@@ -5254,32 +5337,32 @@
       <c r="A113" s="2">
         <v>191149.0</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G113" s="2" t="s">
+      <c r="B113" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G113" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H113" s="2">
         <v>22.8</v>
       </c>
-      <c r="I113" s="3">
+      <c r="I113" s="7">
         <v>41675.0</v>
       </c>
-      <c r="J113" s="2" t="s">
-        <v>227</v>
+      <c r="J113" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="K113" s="2">
         <v>4.0</v>
@@ -5289,32 +5372,32 @@
       <c r="A114" s="2">
         <v>191172.0</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G114" s="2" t="s">
+      <c r="B114" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G114" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H114" s="2">
         <v>9.0</v>
       </c>
-      <c r="I114" s="3">
+      <c r="I114" s="7">
         <v>42009.0</v>
       </c>
-      <c r="J114" s="2" t="s">
-        <v>227</v>
+      <c r="J114" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="K114" s="2">
         <v>4.0</v>
@@ -5324,32 +5407,32 @@
       <c r="A115" s="2">
         <v>191153.0</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G115" s="2" t="s">
+      <c r="B115" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G115" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H115" s="2">
         <v>20.0</v>
       </c>
-      <c r="I115" s="3">
+      <c r="I115" s="8">
         <v>41989.0</v>
       </c>
-      <c r="J115" s="2" t="s">
-        <v>227</v>
+      <c r="J115" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="K115" s="2">
         <v>4.0</v>
@@ -5359,32 +5442,32 @@
       <c r="A116" s="2">
         <v>191175.0</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G116" s="2" t="s">
+      <c r="B116" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G116" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H116" s="2">
         <v>12.0</v>
       </c>
-      <c r="I116" s="3">
+      <c r="I116" s="7">
         <v>42461.0</v>
       </c>
-      <c r="J116" s="2" t="s">
-        <v>227</v>
+      <c r="J116" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="K116" s="2">
         <v>4.0</v>
@@ -5394,31 +5477,31 @@
       <c r="A117" s="2">
         <v>191056.0</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G117" s="2" t="s">
+      <c r="B117" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G117" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H117" s="2">
         <v>246.0</v>
       </c>
-      <c r="I117" s="3">
+      <c r="I117" s="7">
         <v>38107.0</v>
       </c>
-      <c r="J117" s="2" t="s">
+      <c r="J117" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K117" s="2">
@@ -5429,31 +5512,31 @@
       <c r="A118" s="2">
         <v>192026.0</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G118" s="2" t="s">
+      <c r="B118" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G118" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H118" s="2">
         <v>443.99</v>
       </c>
-      <c r="I118" s="3">
+      <c r="I118" s="8">
         <v>39811.0</v>
       </c>
-      <c r="J118" s="2" t="s">
+      <c r="J118" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K118" s="2">
@@ -5464,31 +5547,31 @@
       <c r="A119" s="2">
         <v>191058.0</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G119" s="2" t="s">
+      <c r="B119" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G119" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H119" s="2">
         <v>405.75</v>
       </c>
-      <c r="I119" s="3">
+      <c r="I119" s="7">
         <v>40009.0</v>
       </c>
-      <c r="J119" s="2" t="s">
+      <c r="J119" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K119" s="2">
@@ -5499,31 +5582,31 @@
       <c r="A120" s="2">
         <v>191004.0</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G120" s="2" t="s">
+      <c r="B120" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G120" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H120" s="2">
         <v>258.08</v>
       </c>
-      <c r="I120" s="3">
+      <c r="I120" s="7">
         <v>13881.0</v>
       </c>
-      <c r="J120" s="2" t="s">
+      <c r="J120" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K120" s="2">
@@ -5534,31 +5617,31 @@
       <c r="A121" s="2">
         <v>191062.0</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G121" s="2" t="s">
+      <c r="B121" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G121" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H121" s="2">
         <v>278.0</v>
       </c>
-      <c r="I121" s="3">
+      <c r="I121" s="7">
         <v>34886.0</v>
       </c>
-      <c r="J121" s="2" t="s">
+      <c r="J121" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K121" s="2">
@@ -5569,31 +5652,31 @@
       <c r="A122" s="2">
         <v>191029.0</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E122" s="2" t="s">
+      <c r="B122" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F122" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G122" s="2" t="s">
+      <c r="F122" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G122" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H122" s="2">
         <v>296.0</v>
       </c>
-      <c r="I122" s="3">
+      <c r="I122" s="8">
         <v>37986.0</v>
       </c>
-      <c r="J122" s="2" t="s">
+      <c r="J122" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K122" s="2">
@@ -5604,31 +5687,31 @@
       <c r="A123" s="2">
         <v>191120.0</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E123" s="2" t="s">
+      <c r="B123" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E123" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F123" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G123" s="2" t="s">
+      <c r="F123" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G123" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H123" s="2">
         <v>300.0</v>
       </c>
-      <c r="I123" s="3">
+      <c r="I123" s="7">
         <v>41332.0</v>
       </c>
-      <c r="J123" s="2" t="s">
+      <c r="J123" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K123" s="2">
@@ -5639,31 +5722,31 @@
       <c r="A124" s="2">
         <v>191035.0</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G124" s="2" t="s">
+      <c r="B124" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G124" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H124" s="2">
         <v>415.54</v>
       </c>
-      <c r="I124" s="3">
+      <c r="I124" s="7">
         <v>22118.0</v>
       </c>
-      <c r="J124" s="2" t="s">
+      <c r="J124" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K124" s="2">
@@ -5674,31 +5757,31 @@
       <c r="A125" s="2">
         <v>191169.0</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E125" s="2" t="s">
+      <c r="B125" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E125" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F125" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G125" s="2" t="s">
+      <c r="F125" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G125" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H125" s="2">
         <v>37.48</v>
       </c>
-      <c r="I125" s="3">
+      <c r="I125" s="8">
         <v>43070.0</v>
       </c>
-      <c r="J125" s="2" t="s">
+      <c r="J125" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K125" s="2">
@@ -5709,25 +5792,25 @@
       <c r="A126" s="2">
         <v>193071.0</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
-      <c r="F126" s="2"/>
-      <c r="G126" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="I126" s="3">
+      <c r="B126" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D126" s="6"/>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H126" s="3">
+        <v>11.36</v>
+      </c>
+      <c r="I126" s="7">
         <v>41463.0</v>
       </c>
-      <c r="J126" s="2" t="s">
+      <c r="J126" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K126" s="2">
@@ -5738,25 +5821,25 @@
       <c r="A127" s="2">
         <v>193066.0</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
-      <c r="F127" s="2"/>
-      <c r="G127" s="2" t="s">
+      <c r="B127" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D127" s="6"/>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H127" s="2">
         <v>350.0</v>
       </c>
-      <c r="I127" s="3">
+      <c r="I127" s="7">
         <v>41155.0</v>
       </c>
-      <c r="J127" s="2" t="s">
+      <c r="J127" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K127" s="2">
@@ -5767,21 +5850,21 @@
       <c r="A128" s="2">
         <v>193084.0</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
-      <c r="F128" s="2"/>
-      <c r="G128" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H128" s="2"/>
-      <c r="I128" s="3"/>
-      <c r="J128" s="2" t="s">
+      <c r="B128" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D128" s="6"/>
+      <c r="E128" s="6"/>
+      <c r="F128" s="6"/>
+      <c r="G128" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H128" s="6"/>
+      <c r="I128" s="6"/>
+      <c r="J128" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K128" s="2">
@@ -5792,31 +5875,31 @@
       <c r="A129" s="2">
         <v>191090.0</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G129" s="2" t="s">
+      <c r="B129" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G129" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H129" s="2">
         <v>44.61</v>
       </c>
-      <c r="I129" s="3">
+      <c r="I129" s="7">
         <v>42143.0</v>
       </c>
-      <c r="J129" s="2" t="s">
+      <c r="J129" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K129" s="2">
@@ -5827,29 +5910,31 @@
       <c r="A130" s="2">
         <v>191173.0</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G130" s="2" t="s">
+      <c r="B130" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G130" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H130" s="2">
         <v>30.0</v>
       </c>
-      <c r="I130" s="3">
+      <c r="I130" s="7">
         <v>42740.0</v>
       </c>
-      <c r="J130" s="2" t="s">
+      <c r="J130" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K130" s="2">
@@ -5860,31 +5945,31 @@
       <c r="A131" s="2">
         <v>191020.0</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G131" s="2" t="s">
+      <c r="B131" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G131" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H131" s="2">
         <v>201.62</v>
       </c>
-      <c r="I131" s="3">
+      <c r="I131" s="8">
         <v>37921.0</v>
       </c>
-      <c r="J131" s="2" t="s">
+      <c r="J131" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K131" s="2">
@@ -5895,21 +5980,21 @@
       <c r="A132" s="2">
         <v>191160.0</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H132" s="2"/>
-      <c r="I132" s="3"/>
-      <c r="J132" s="2" t="s">
+      <c r="B132" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H132" s="6"/>
+      <c r="I132" s="6"/>
+      <c r="J132" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K132" s="2">
@@ -5920,21 +6005,21 @@
       <c r="A133" s="2">
         <v>193012.0</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
-      <c r="F133" s="2"/>
-      <c r="G133" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H133" s="2"/>
-      <c r="I133" s="3"/>
-      <c r="J133" s="2" t="s">
+      <c r="B133" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D133" s="6"/>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H133" s="6"/>
+      <c r="I133" s="6"/>
+      <c r="J133" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K133" s="2">
@@ -5945,21 +6030,21 @@
       <c r="A134" s="2">
         <v>193022.0</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
-      <c r="F134" s="2"/>
-      <c r="G134" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H134" s="2"/>
-      <c r="I134" s="3"/>
-      <c r="J134" s="2" t="s">
+      <c r="B134" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D134" s="6"/>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H134" s="6"/>
+      <c r="I134" s="6"/>
+      <c r="J134" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K134" s="2">
@@ -5970,31 +6055,31 @@
       <c r="A135" s="2">
         <v>191017.0</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E135" s="2" t="s">
+      <c r="B135" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E135" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F135" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G135" s="2" t="s">
+      <c r="F135" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G135" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H135" s="2">
         <v>318.0</v>
       </c>
-      <c r="I135" s="3">
+      <c r="I135" s="8">
         <v>37604.0</v>
       </c>
-      <c r="J135" s="2" t="s">
+      <c r="J135" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K135" s="2">
@@ -6005,31 +6090,31 @@
       <c r="A136" s="2">
         <v>192081.0</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G136" s="2" t="s">
+      <c r="B136" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G136" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H136" s="2">
         <v>579.56</v>
       </c>
-      <c r="I136" s="3">
+      <c r="I136" s="7">
         <v>32601.0</v>
       </c>
-      <c r="J136" s="2" t="s">
+      <c r="J136" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K136" s="2">
@@ -6040,31 +6125,31 @@
       <c r="A137" s="2">
         <v>191021.0</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G137" s="2" t="s">
+      <c r="B137" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G137" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H137" s="2">
         <v>252.0</v>
       </c>
-      <c r="I137" s="3">
+      <c r="I137" s="7">
         <v>38124.0</v>
       </c>
-      <c r="J137" s="2" t="s">
+      <c r="J137" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K137" s="2">
@@ -6075,32 +6160,32 @@
       <c r="A138" s="2">
         <v>191052.0</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G138" s="2" t="s">
+      <c r="B138" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G138" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H138" s="2">
         <v>612.0</v>
       </c>
-      <c r="I138" s="3">
+      <c r="I138" s="7">
         <v>35247.0</v>
       </c>
-      <c r="J138" s="2" t="s">
-        <v>207</v>
+      <c r="J138" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="K138" s="2">
         <v>4.0</v>
@@ -6110,31 +6195,31 @@
       <c r="A139" s="2">
         <v>191063.0</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E139" s="2" t="s">
+      <c r="B139" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E139" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F139" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G139" s="2" t="s">
+      <c r="F139" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G139" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H139" s="2">
         <v>257.0</v>
       </c>
-      <c r="I139" s="3">
+      <c r="I139" s="7">
         <v>39640.0</v>
       </c>
-      <c r="J139" s="2" t="s">
+      <c r="J139" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K139" s="2">
@@ -6145,31 +6230,31 @@
       <c r="A140" s="2">
         <v>191036.0</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G140" s="2" t="s">
+      <c r="B140" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G140" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H140" s="2">
         <v>321.0</v>
       </c>
-      <c r="I140" s="3">
+      <c r="I140" s="8">
         <v>39385.0</v>
       </c>
-      <c r="J140" s="2" t="s">
+      <c r="J140" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K140" s="2">
@@ -6180,31 +6265,31 @@
       <c r="A141" s="2">
         <v>191030.0</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E141" s="2" t="s">
+      <c r="B141" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E141" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F141" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G141" s="2" t="s">
+      <c r="F141" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G141" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H141" s="2">
         <v>358.57</v>
       </c>
-      <c r="I141" s="3">
+      <c r="I141" s="7">
         <v>21968.0</v>
       </c>
-      <c r="J141" s="2" t="s">
+      <c r="J141" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K141" s="2">
@@ -6215,32 +6300,32 @@
       <c r="A142" s="2">
         <v>191049.0</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E142" s="2" t="s">
+      <c r="B142" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E142" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F142" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G142" s="2" t="s">
+      <c r="F142" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G142" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H142" s="2">
         <v>52.0</v>
       </c>
-      <c r="I142" s="3">
+      <c r="I142" s="7">
         <v>39534.0</v>
       </c>
-      <c r="J142" s="2" t="s">
-        <v>227</v>
+      <c r="J142" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="K142" s="2">
         <v>4.0</v>
@@ -6250,31 +6335,31 @@
       <c r="A143" s="2">
         <v>191147.0</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="E143" s="2" t="s">
+      <c r="B143" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E143" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F143" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G143" s="2" t="s">
+      <c r="F143" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G143" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H143" s="2">
         <v>279.87</v>
       </c>
-      <c r="I143" s="3">
+      <c r="I143" s="7">
         <v>41400.0</v>
       </c>
-      <c r="J143" s="2" t="s">
+      <c r="J143" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K143" s="2">
@@ -6285,31 +6370,31 @@
       <c r="A144" s="2">
         <v>191108.0</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E144" s="2" t="s">
+      <c r="B144" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E144" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F144" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G144" s="2" t="s">
+      <c r="F144" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G144" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H144" s="2">
         <v>278.0</v>
       </c>
-      <c r="I144" s="3">
+      <c r="I144" s="8">
         <v>40856.0</v>
       </c>
-      <c r="J144" s="2" t="s">
+      <c r="J144" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K144" s="2">
@@ -6320,31 +6405,31 @@
       <c r="A145" s="2">
         <v>191038.0</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E145" s="2" t="s">
+      <c r="B145" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E145" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F145" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G145" s="2" t="s">
+      <c r="F145" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G145" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H145" s="2">
         <v>556.0</v>
       </c>
-      <c r="I145" s="3">
+      <c r="I145" s="7">
         <v>32601.0</v>
       </c>
-      <c r="J145" s="2" t="s">
+      <c r="J145" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K145" s="2">
@@ -6355,31 +6440,31 @@
       <c r="A146" s="2">
         <v>191019.0</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G146" s="2" t="s">
+      <c r="B146" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G146" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H146" s="2">
         <v>278.44</v>
       </c>
-      <c r="I146" s="3">
+      <c r="I146" s="7">
         <v>39652.0</v>
       </c>
-      <c r="J146" s="2" t="s">
+      <c r="J146" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K146" s="2">
@@ -6390,31 +6475,31 @@
       <c r="A147" s="2">
         <v>191053.0</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E147" s="2" t="s">
+      <c r="B147" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E147" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F147" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G147" s="2" t="s">
+      <c r="F147" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G147" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H147" s="2">
         <v>200.0</v>
       </c>
-      <c r="I147" s="3">
+      <c r="I147" s="7">
         <v>39647.0</v>
       </c>
-      <c r="J147" s="2" t="s">
+      <c r="J147" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K147" s="2">
@@ -6425,21 +6510,21 @@
       <c r="A148" s="2">
         <v>191026.0</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
-      <c r="F148" s="2"/>
-      <c r="G148" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H148" s="2"/>
-      <c r="I148" s="3"/>
-      <c r="J148" s="2" t="s">
+      <c r="B148" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D148" s="6"/>
+      <c r="E148" s="6"/>
+      <c r="F148" s="6"/>
+      <c r="G148" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H148" s="6"/>
+      <c r="I148" s="6"/>
+      <c r="J148" s="3" t="s">
         <v>136</v>
       </c>
       <c r="K148" s="2">
@@ -6450,31 +6535,31 @@
       <c r="A149" s="2">
         <v>191059.0</v>
       </c>
-      <c r="B149" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E149" s="2" t="s">
+      <c r="B149" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E149" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F149" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G149" s="2" t="s">
+      <c r="F149" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G149" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H149" s="2">
         <v>281.3</v>
       </c>
-      <c r="I149" s="3">
+      <c r="I149" s="8">
         <v>39772.0</v>
       </c>
-      <c r="J149" s="2" t="s">
+      <c r="J149" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K149" s="2">
@@ -6485,31 +6570,31 @@
       <c r="A150" s="2">
         <v>191043.0</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G150" s="2" t="s">
+      <c r="B150" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G150" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H150" s="2">
         <v>344.26</v>
       </c>
-      <c r="I150" s="3">
+      <c r="I150" s="8">
         <v>39780.0</v>
       </c>
-      <c r="J150" s="2" t="s">
+      <c r="J150" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K150" s="2">
@@ -6520,31 +6605,31 @@
       <c r="A151" s="2">
         <v>191097.0</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E151" s="2" t="s">
+      <c r="B151" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E151" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F151" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G151" s="2" t="s">
+      <c r="F151" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G151" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H151" s="2">
         <v>422.86</v>
       </c>
-      <c r="I151" s="3">
+      <c r="I151" s="7">
         <v>38180.0</v>
       </c>
-      <c r="J151" s="2" t="s">
+      <c r="J151" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K151" s="2">
@@ -6552,76 +6637,84 @@
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="5">
+      <c r="A152" s="2">
         <v>999920.0</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>358</v>
-      </c>
+      <c r="B152" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D152" s="6"/>
+      <c r="E152" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="H152" s="6"/>
       <c r="I152" s="6"/>
-      <c r="J152" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="J152" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K152" s="6"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
       <c r="A153" s="2">
         <v>999999.0</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>135</v>
-      </c>
+      <c r="B153" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D153" s="6"/>
+      <c r="E153" s="6"/>
+      <c r="F153" s="6"/>
+      <c r="G153" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H153" s="6"/>
       <c r="I153" s="6"/>
-      <c r="J153" s="2" t="s">
+      <c r="J153" s="3" t="s">
         <v>136</v>
       </c>
+      <c r="K153" s="6"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
       <c r="A154" s="2">
         <v>485000.0</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="G154" s="2" t="s">
-        <v>364</v>
+      <c r="B154" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>371</v>
       </c>
       <c r="H154" s="2">
         <v>301.95</v>
       </c>
-      <c r="I154" s="3">
+      <c r="I154" s="7">
         <v>36526.0</v>
       </c>
-      <c r="J154" s="2" t="s">
+      <c r="J154" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K154" s="2">
@@ -6632,30 +6725,30 @@
       <c r="A155" s="2">
         <v>430001.0</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C155" s="2" t="s">
+      <c r="B155" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C155" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D155" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>369</v>
+      <c r="D155" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="H155" s="2">
         <v>60.0</v>
       </c>
-      <c r="I155" s="3"/>
-      <c r="J155" s="2" t="s">
-        <v>227</v>
+      <c r="I155" s="6"/>
+      <c r="J155" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="K155" s="2">
         <v>2.0</v>
@@ -6665,31 +6758,31 @@
       <c r="A156" s="2">
         <v>385000.0</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C156" s="2" t="s">
+      <c r="B156" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C156" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D156" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>369</v>
+      <c r="D156" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="H156" s="2">
         <v>616.0</v>
       </c>
-      <c r="I156" s="3">
+      <c r="I156" s="8">
         <v>33878.0</v>
       </c>
-      <c r="J156" s="2" t="s">
+      <c r="J156" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K156" s="2">
@@ -6700,31 +6793,31 @@
       <c r="A157" s="2">
         <v>430000.0</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C157" s="2" t="s">
+      <c r="B157" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C157" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D157" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F157" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>369</v>
+      <c r="D157" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="H157" s="2">
         <v>377.85</v>
       </c>
-      <c r="I157" s="3">
+      <c r="I157" s="7">
         <v>30109.0</v>
       </c>
-      <c r="J157" s="2" t="s">
+      <c r="J157" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K157" s="2">
@@ -6735,31 +6828,31 @@
       <c r="A158" s="2">
         <v>385001.0</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C158" s="2" t="s">
+      <c r="B158" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C158" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D158" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E158" s="2" t="s">
+      <c r="D158" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F158" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="F158" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>369</v>
+      <c r="G158" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="H158" s="2">
         <v>412.04</v>
       </c>
-      <c r="I158" s="3">
+      <c r="I158" s="7">
         <v>35958.0</v>
       </c>
-      <c r="J158" s="2" t="s">
+      <c r="J158" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K158" s="2">
@@ -6770,31 +6863,31 @@
       <c r="A159" s="2">
         <v>405005.0</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="C159" s="2" t="s">
+      <c r="B159" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C159" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D159" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F159" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>382</v>
+      <c r="D159" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>387</v>
       </c>
       <c r="H159" s="2">
         <v>455.84</v>
       </c>
-      <c r="I159" s="3">
+      <c r="I159" s="7">
         <v>41655.0</v>
       </c>
-      <c r="J159" s="2" t="s">
+      <c r="J159" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K159" s="2">
@@ -6805,31 +6898,31 @@
       <c r="A160" s="2">
         <v>405000.0</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="C160" s="2" t="s">
+      <c r="B160" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C160" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D160" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="F160" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>382</v>
+      <c r="D160" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>387</v>
       </c>
       <c r="H160" s="2">
         <v>1129.51</v>
       </c>
-      <c r="I160" s="3">
+      <c r="I160" s="7">
         <v>1960.0</v>
       </c>
-      <c r="J160" s="2" t="s">
+      <c r="J160" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K160" s="2">
@@ -6840,29 +6933,29 @@
       <c r="A161" s="2">
         <v>495000.0</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="C161" s="2" t="s">
+      <c r="B161" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C161" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D161" s="2" t="s">
+      <c r="D161" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E161" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="E161" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G161" s="2" t="s">
-        <v>382</v>
+      <c r="F161" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>387</v>
       </c>
       <c r="H161" s="2">
         <v>412.05</v>
       </c>
-      <c r="I161" s="3"/>
-      <c r="J161" s="2" t="s">
+      <c r="I161" s="6"/>
+      <c r="J161" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K161" s="2">
@@ -6873,31 +6966,31 @@
       <c r="A162" s="2">
         <v>405003.0</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C162" s="2" t="s">
+      <c r="B162" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C162" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D162" s="2" t="s">
+      <c r="D162" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E162" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="E162" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="F162" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G162" s="2" t="s">
-        <v>382</v>
+      <c r="F162" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>387</v>
       </c>
       <c r="H162" s="2">
         <v>487.04</v>
       </c>
-      <c r="I162" s="3">
+      <c r="I162" s="7">
         <v>39636.0</v>
       </c>
-      <c r="J162" s="2" t="s">
+      <c r="J162" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K162" s="2">
@@ -6908,31 +7001,31 @@
       <c r="A163" s="2">
         <v>540004.0</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F163" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="G163" s="2" t="s">
-        <v>394</v>
+      <c r="B163" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>399</v>
       </c>
       <c r="H163" s="2">
         <v>690.0</v>
       </c>
-      <c r="I163" s="3">
+      <c r="I163" s="7">
         <v>41288.0</v>
       </c>
-      <c r="J163" s="2" t="s">
+      <c r="J163" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K163" s="2">
@@ -6943,31 +7036,31 @@
       <c r="A164" s="2">
         <v>540002.0</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D164" s="2" t="s">
+      <c r="B164" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C164" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="E164" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="F164" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="G164" s="2" t="s">
-        <v>394</v>
+      <c r="D164" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>399</v>
       </c>
       <c r="H164" s="2">
         <v>350.0</v>
       </c>
-      <c r="I164" s="3">
+      <c r="I164" s="7">
         <v>39566.0</v>
       </c>
-      <c r="J164" s="2" t="s">
+      <c r="J164" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K164" s="2">
@@ -6978,29 +7071,29 @@
       <c r="A165" s="2">
         <v>540000.0</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="G165" s="2" t="s">
-        <v>394</v>
+      <c r="B165" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>399</v>
       </c>
       <c r="H165" s="2">
         <v>1177.02</v>
       </c>
-      <c r="I165" s="3"/>
-      <c r="J165" s="2" t="s">
+      <c r="I165" s="6"/>
+      <c r="J165" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K165" s="2">
@@ -7011,39 +7104,159 @@
       <c r="A166" s="2">
         <v>565000.0</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D166" s="2" t="s">
+      <c r="B166" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="G166" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="F166" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="G166" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="H166" s="2">
         <v>120.0</v>
       </c>
-      <c r="I166" s="3"/>
-      <c r="J166" s="2" t="s">
-        <v>227</v>
+      <c r="I166" s="6"/>
+      <c r="J166" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="K166" s="2">
         <v>2.0</v>
       </c>
     </row>
-    <row r="167" ht="14.25" customHeight="1"/>
-    <row r="168" ht="14.25" customHeight="1"/>
-    <row r="169" ht="14.25" customHeight="1"/>
-    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1">
+      <c r="A167" s="2">
+        <v>566000.0</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H167" s="2">
+        <v>210.05</v>
+      </c>
+      <c r="I167" s="6"/>
+      <c r="J167" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K167" s="6"/>
+    </row>
+    <row r="168" ht="14.25" customHeight="1">
+      <c r="A168" s="2">
+        <v>567000.0</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H168" s="2">
+        <v>150.0</v>
+      </c>
+      <c r="I168" s="6"/>
+      <c r="J168" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K168" s="6"/>
+    </row>
+    <row r="169" ht="14.25" customHeight="1">
+      <c r="A169" s="2">
+        <v>568000.0</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H169" s="2">
+        <v>128.6</v>
+      </c>
+      <c r="I169" s="6"/>
+      <c r="J169" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K169" s="6"/>
+    </row>
+    <row r="170" ht="14.25" customHeight="1">
+      <c r="A170" s="2">
+        <v>569000.0</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H170" s="2">
+        <v>264.12</v>
+      </c>
+      <c r="I170" s="6"/>
+      <c r="J170" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K170" s="6"/>
+    </row>
     <row r="171" ht="14.25" customHeight="1"/>
     <row r="172" ht="14.25" customHeight="1"/>
     <row r="173" ht="14.25" customHeight="1"/>
@@ -7661,223 +7874,10 @@
     <row r="785" ht="14.25" customHeight="1"/>
     <row r="786" ht="14.25" customHeight="1"/>
     <row r="787" ht="14.25" customHeight="1"/>
-    <row r="788" ht="14.25" customHeight="1"/>
-    <row r="789" ht="14.25" customHeight="1"/>
-    <row r="790" ht="14.25" customHeight="1"/>
-    <row r="791" ht="14.25" customHeight="1"/>
-    <row r="792" ht="14.25" customHeight="1"/>
-    <row r="793" ht="14.25" customHeight="1"/>
-    <row r="794" ht="14.25" customHeight="1"/>
-    <row r="795" ht="14.25" customHeight="1"/>
-    <row r="796" ht="14.25" customHeight="1"/>
-    <row r="797" ht="14.25" customHeight="1"/>
-    <row r="798" ht="14.25" customHeight="1"/>
-    <row r="799" ht="14.25" customHeight="1"/>
-    <row r="800" ht="14.25" customHeight="1"/>
-    <row r="801" ht="14.25" customHeight="1"/>
-    <row r="802" ht="14.25" customHeight="1"/>
-    <row r="803" ht="14.25" customHeight="1"/>
-    <row r="804" ht="14.25" customHeight="1"/>
-    <row r="805" ht="14.25" customHeight="1"/>
-    <row r="806" ht="14.25" customHeight="1"/>
-    <row r="807" ht="14.25" customHeight="1"/>
-    <row r="808" ht="14.25" customHeight="1"/>
-    <row r="809" ht="14.25" customHeight="1"/>
-    <row r="810" ht="14.25" customHeight="1"/>
-    <row r="811" ht="14.25" customHeight="1"/>
-    <row r="812" ht="14.25" customHeight="1"/>
-    <row r="813" ht="14.25" customHeight="1"/>
-    <row r="814" ht="14.25" customHeight="1"/>
-    <row r="815" ht="14.25" customHeight="1"/>
-    <row r="816" ht="14.25" customHeight="1"/>
-    <row r="817" ht="14.25" customHeight="1"/>
-    <row r="818" ht="14.25" customHeight="1"/>
-    <row r="819" ht="14.25" customHeight="1"/>
-    <row r="820" ht="14.25" customHeight="1"/>
-    <row r="821" ht="14.25" customHeight="1"/>
-    <row r="822" ht="14.25" customHeight="1"/>
-    <row r="823" ht="14.25" customHeight="1"/>
-    <row r="824" ht="14.25" customHeight="1"/>
-    <row r="825" ht="14.25" customHeight="1"/>
-    <row r="826" ht="14.25" customHeight="1"/>
-    <row r="827" ht="14.25" customHeight="1"/>
-    <row r="828" ht="14.25" customHeight="1"/>
-    <row r="829" ht="14.25" customHeight="1"/>
-    <row r="830" ht="14.25" customHeight="1"/>
-    <row r="831" ht="14.25" customHeight="1"/>
-    <row r="832" ht="14.25" customHeight="1"/>
-    <row r="833" ht="14.25" customHeight="1"/>
-    <row r="834" ht="14.25" customHeight="1"/>
-    <row r="835" ht="14.25" customHeight="1"/>
-    <row r="836" ht="14.25" customHeight="1"/>
-    <row r="837" ht="14.25" customHeight="1"/>
-    <row r="838" ht="14.25" customHeight="1"/>
-    <row r="839" ht="14.25" customHeight="1"/>
-    <row r="840" ht="14.25" customHeight="1"/>
-    <row r="841" ht="14.25" customHeight="1"/>
-    <row r="842" ht="14.25" customHeight="1"/>
-    <row r="843" ht="14.25" customHeight="1"/>
-    <row r="844" ht="14.25" customHeight="1"/>
-    <row r="845" ht="14.25" customHeight="1"/>
-    <row r="846" ht="14.25" customHeight="1"/>
-    <row r="847" ht="14.25" customHeight="1"/>
-    <row r="848" ht="14.25" customHeight="1"/>
-    <row r="849" ht="14.25" customHeight="1"/>
-    <row r="850" ht="14.25" customHeight="1"/>
-    <row r="851" ht="14.25" customHeight="1"/>
-    <row r="852" ht="14.25" customHeight="1"/>
-    <row r="853" ht="14.25" customHeight="1"/>
-    <row r="854" ht="14.25" customHeight="1"/>
-    <row r="855" ht="14.25" customHeight="1"/>
-    <row r="856" ht="14.25" customHeight="1"/>
-    <row r="857" ht="14.25" customHeight="1"/>
-    <row r="858" ht="14.25" customHeight="1"/>
-    <row r="859" ht="14.25" customHeight="1"/>
-    <row r="860" ht="14.25" customHeight="1"/>
-    <row r="861" ht="14.25" customHeight="1"/>
-    <row r="862" ht="14.25" customHeight="1"/>
-    <row r="863" ht="14.25" customHeight="1"/>
-    <row r="864" ht="14.25" customHeight="1"/>
-    <row r="865" ht="14.25" customHeight="1"/>
-    <row r="866" ht="14.25" customHeight="1"/>
-    <row r="867" ht="14.25" customHeight="1"/>
-    <row r="868" ht="14.25" customHeight="1"/>
-    <row r="869" ht="14.25" customHeight="1"/>
-    <row r="870" ht="14.25" customHeight="1"/>
-    <row r="871" ht="14.25" customHeight="1"/>
-    <row r="872" ht="14.25" customHeight="1"/>
-    <row r="873" ht="14.25" customHeight="1"/>
-    <row r="874" ht="14.25" customHeight="1"/>
-    <row r="875" ht="14.25" customHeight="1"/>
-    <row r="876" ht="14.25" customHeight="1"/>
-    <row r="877" ht="14.25" customHeight="1"/>
-    <row r="878" ht="14.25" customHeight="1"/>
-    <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
-    <row r="989" ht="14.25" customHeight="1"/>
-    <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
-    <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$K$166">
-    <sortState ref="A1:K166">
-      <sortCondition ref="G1:G166"/>
+  <autoFilter ref="$A$1:$K$170">
+    <sortState ref="A1:K170">
+      <sortCondition ref="G1:G170"/>
     </sortState>
   </autoFilter>
   <printOptions/>
